--- a/UyumsuzluklarTarama_Gunluk_061026.xlsx
+++ b/UyumsuzluklarTarama_Gunluk_061026.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.93</v>
+        <v>8.94</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/UyumsuzluklarTarama_Gunluk_061026.xlsx
+++ b/UyumsuzluklarTarama_Gunluk_061026.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Taze_Sinyaller" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bugun'!$A$1:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tum_Sonuclar'!$A$1:$AC$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Alim_Satim'!$A$1:$K$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Taze_Sinyaller'!$A$1:$O$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Bugun'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tum_Sonuclar'!$A$1:$AC$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Alim_Satim'!$A$1:$K$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Taze_Sinyaller'!$A$1:$O$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -442,13 +442,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -530,62 +530,518 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ATR:HID BEAR, CCI:HID BEAR, Chaikin:HID BEAR, MOM:HID BEAR, ROC:HID BEAR, Williams %R:HID BEAR</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>AAGYO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>06-10-26</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C3" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>UYUMSUZLUK</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>RSI:HID BEAR, CCI:HID BEAR, Chaikin:HID BEAR, Williams %R:HID BEAR</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CMO:HID BEAR, CCI:HID BEAR, Chaikin:HID BEAR, RSI:HID BEAR, Williams %R:HID BEAR</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K3" t="n">
+        <v>80</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>YÜKSEK</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>6</v>
+      <c r="M3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AKFIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CCI:HID BEAR, RSI:HID BEAR, Williams %R:HID BEAR</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>70</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ALCAR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>608.5</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MFI:REG BULL</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>80</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ALARK</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>105</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MACD:HID BULL</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AKSGY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MOM:HID BEAR</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALFAS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Williams %R:HID BEAR</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK + KIRILIM</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MACD:REG BULL</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>DİRENÇ↑</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AKBNK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>MACD:HID BULL</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>KARMA</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M2"/>
+  <autoFilter ref="A1:M10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -596,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -607,7 +1063,7 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
@@ -618,8 +1074,8 @@
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
     <col width="38" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
     <col width="38" customWidth="1" min="22" max="22"/>
     <col width="11" customWidth="1" min="23" max="23"/>
     <col width="11" customWidth="1" min="24" max="24"/>
@@ -798,18 +1254,18 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>KARMA</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>83.33</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>83.33</v>
+        <v>50</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>YÜKSEK</t>
+          <t>DÜŞÜK</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -842,19 +1298,19 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>09-09-26</t>
+          <t>01-10-26</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>ATR, CMO, MOM, ROC, RSI</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -873,13 +1329,13 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -917,7 +1373,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -925,10 +1381,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="G3" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -977,7 +1433,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Chaikin, MFI</t>
+          <t>ATR, Chaikin, MFI</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -987,22 +1443,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADX</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>RSI, MACD, CCI, Stochastic</t>
+          <t>CCI, MACD, RSI, Stochastic</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
@@ -1040,7 +1496,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.94</v>
+        <v>8.92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1048,10 +1504,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="G4" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1072,14 +1528,14 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>RSI:HID BEAR, CCI:HID BEAR, Chaikin:HID BEAR, Williams %R:HID BEAR</t>
+          <t>CMO:HID BEAR, CCI:HID BEAR, Chaikin:HID BEAR, RSI:HID BEAR, Williams %R:HID BEAR</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1100,7 +1556,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>MACD</t>
+          <t>MACD, ROC</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1115,17 +1571,17 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>RSI, CCI, Chaikin, MFI, Williams %R</t>
+          <t>ADX, CMO, CCI, Chaikin, MFI, MOM, RSI, Williams %R</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
@@ -1163,7 +1619,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>89.15000000000001</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1171,10 +1627,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1223,7 +1679,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>MACD, Chaikin, OBV, Stochastic</t>
+          <t>Chaikin, MACD, MOM, OBV, Stochastic</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1242,13 +1698,13 @@
         </is>
       </c>
       <c r="W5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X5" t="n">
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
@@ -1286,7 +1742,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>24.9</v>
+        <v>24.92</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,7 +1802,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>MACD, CCI, Chaikin, MFI, Stochastic, Williams %R</t>
+          <t>CCI, Chaikin, MACD, MFI, Stochastic, Williams %R</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1392,8 +1848,4313 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADESE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>01-10-26</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>CCI, MFI, Williams %R</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Düşen kanal</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>6 temas (Güçlü) | 05-02-26 → 01-10-26 | Skor=0.843 [temas 0.75, güncellik 1.0, uzunluk 0.54, fit 0.784, yakınlık 1.0] | Temaslar: 05-02-26, 02-03-26, 09-03-26, 27-03-26, 07-04-26, 01-10-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 14-07-26 → 09-09-26 | Skor=0.781 [temas 0.667, güncellik 1.0, uzunluk 0.133, fit 0.744, yakınlık 1.0] | Temaslar: 14-07-26, 23-07-26, 12-08-26, 09-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADGYO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G8" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>24-09-26</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>CCI, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>ATR, Chaikin</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>İnen üçgen (descending triangle)</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>7 temas (Güçlü) | 17-11-25 → 30-09-26 | Skor=0.857 [temas 0.778, güncellik 1.0, uzunluk 0.727, fit 0.709, yakınlık 1.0] | Temaslar: 17-11-25, 24-11-25, 05-12-25, 24-12-25, 30-12-25, 21-09-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 25-08-26 → 24-09-26 | Skor=0.679 [temas 0.5, güncellik 1.0, uzunluk 0.073, fit 0.5, yakınlık 1.0] | Temaslar: 25-08-26, 24-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="G9" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK + KIRILIM</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>MACD:REG BULL</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>DİRENÇ↑</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MACD, MFI, OBV, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ADX, CCI, MOM, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>İnen üçgen (descending triangle)</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>7 temas (Güçlü) | 30-12-25 → 16-09-26 | Skor=0.843 [temas 0.778, güncellik 1.0, uzunluk 0.59, fit 0.638, yakınlık 1.0] | Temaslar: 30-12-25, 09-03-26, 23-03-26, 30-03-26, 02-09-26, 16-09-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 03-08-26 → 11-09-26 | Skor=0.758 [temas 0.6, güncellik 1.0, uzunluk 0.097, fit 0.835, yakınlık 1.0] | Temaslar: 03-08-26, 10-08-26, 11-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AFYON</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Chaikin, MFI</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>3</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Düşen kanal</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 26-06-26 → 30-09-26 | Skor=0.803 [temas 0.714, güncellik 1.0, uzunluk 0.223, fit 0.707, yakınlık 1.0] | Temaslar: 26-06-26, 09-07-26, 30-07-26, 21-09-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 26-03-26 → 09-09-26 | Skor=0.779 [temas 0.6, güncellik 1.0, uzunluk 0.373, fit 0.908, yakınlık 1.0] | Temaslar: 26-03-26, 24-08-26, 09-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AGESA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>238</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G11" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>16-09-26</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>ADX, ATR, CMO, Chaikin, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Stochastic</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>İnen üçgen (descending triangle)</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>9 temas (Güçlü) | 12-12-25 → 01-10-26 | Skor=0.866 [temas 0.818, güncellik 1.0, uzunluk 0.667, fit 0.642, yakınlık 1.0] | Temaslar: 12-12-25, 31-12-25, 06-01-26, 13-01-26, 02-03-26, 09-03-26, 25-03-26, 16-09-26, 01-10-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 01-09-26 → 22-09-26 | Skor=0.741 [temas 0.6, güncellik 1.0, uzunluk 0.05, fit 0.681, yakınlık 1.0] | Temaslar: 01-09-26, 09-09-26, 22-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" t="n">
+        <v>100</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>09-09-26</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>ATR, CMO, CCI, Chaikin, MOM, OBV, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yatay bant / range</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>7 temas (Güçlü) | 20-10-25 → 01-10-26 | Skor=0.849 [temas 0.778, güncellik 1.0, uzunluk 0.793, fit 0.59, yakınlık 1.0] | Temaslar: 20-10-25, 23-03-26, 30-03-26, 07-04-26, 18-08-26, 27-08-26, 01-10-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 14-05-26 → 24-09-26 | Skor=0.821 [temas 0.714, güncellik 1.0, uzunluk 0.3, fit 0.849, yakınlık 1.0] | Temaslar: 14-05-26, 03-08-26, 09-09-26, 18-09-26, 24-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AGROT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G13" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MFI, MOM, RSI</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>CCI, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 19-08-26 → 30-09-26 | Skor=0.761 [temas 0.6, güncellik 1.0, uzunluk 0.1, fit 0.86, yakınlık 1.0] | Temaslar: 19-08-26, 04-09-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 21-08-26 → 15-09-26 | Skor=0.678 [temas 0.5, güncellik 1.0, uzunluk 0.057, fit 0.5, yakınlık 1.0] | Temaslar: 21-08-26, 15-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AGYO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>60</v>
+      </c>
+      <c r="G14" t="n">
+        <v>60</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>29-09-26</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>CMO, Chaikin, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>CCI, MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>6</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>7 temas (Güçlü) | 22-05-26 → 02-10-26 | Skor=0.831 [temas 0.778, güncellik 1.0, uzunluk 0.303, fit 0.657, yakınlık 1.0] | Temaslar: 22-05-26, 10-06-26, 14-07-26, 30-07-26, 06-08-26, 29-09-26, 02-10-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 11-09-26 → 29-09-26 | Skor=0.677 [temas 0.5, güncellik 1.0, uzunluk 0.04, fit 0.5, yakınlık 1.0] | Temaslar: 11-09-26, 29-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AHGAZ</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" t="n">
+        <v>100</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>25-09-26</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>ATR, CMO, MACD, RSI</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MFI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek yukselen, direnç yukselen)</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 22-05-26 → 19-08-26 | Skor=0.590 [temas 0.667, güncellik 0.875, uzunluk 0.197, fit 0.848, yakınlık 0.1] | Temaslar: 22-05-26, 10-06-26, 06-08-26, 19-08-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 10-08-26 → 25-09-26 | Skor=0.819 [temas 0.714, güncellik 1.0, uzunluk 0.113, fit 0.923, yakınlık 1.0] | Temaslar: 10-08-26, 14-08-26, 07-09-26, 16-09-26, 25-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AHSGY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" t="n">
+        <v>100</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>13</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>15-09-26</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>CCI, MACD</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ADX, CMO, Chaikin, MOM, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Düşen kanal</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 13-04-26 → 21-09-26 | Skor=0.778 [temas 0.6, güncellik 1.0, uzunluk 0.36, fit 0.898, yakınlık 1.0] | Temaslar: 13-04-26, 16-04-26, 21-09-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 12-05-26 → 15-09-26 | Skor=0.789 [temas 0.667, güncellik 1.0, uzunluk 0.283, fit 0.75, yakınlık 1.0] | Temaslar: 12-05-26, 03-07-26, 08-07-26, 15-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AKBNK</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>KARMA</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>MACD:HID BULL</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>CCI, MACD, MFI, Stochastic</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>ADX, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>CMO, RSI</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>İnen üçgen (descending triangle)</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 11-11-25 → 16-09-26 | Skor=0.679 [temas 0.667, güncellik 0.958, uzunluk 0.707, fit 0.873, yakınlık 0.322] | Temaslar: 11-11-25, 22-05-26, 30-07-26, 16-09-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 27-02-26 → 22-09-26 | Skor=0.827 [temas 0.714, güncellik 1.0, uzunluk 0.463, fit 0.828, yakınlık 1.0] | Temaslar: 27-02-26, 19-06-26, 25-06-26, 09-09-26, 22-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AKCNS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>22-09-26</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>MACD, MFI, MOM, ROC, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Daralan (simetrik) üçgen</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 24-11-25 → 29-09-26 | Skor=0.829 [temas 0.667, güncellik 1.0, uzunluk 0.707, fit 0.941, yakınlık 1.0] | Temaslar: 24-11-25, 05-12-25, 22-09-26, 29-09-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 08-09-26 → 24-09-26 | Skor=0.677 [temas 0.5, güncellik 1.0, uzunluk 0.04, fit 0.5, yakınlık 1.0] | Temaslar: 08-09-26, 24-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AKENR</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="G19" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin, MFI, MOM, OBV, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>CMO, CCI, ROC, RSI</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>7</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Düşen kanal</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 14-07-26 → 30-09-26 | Skor=0.774 [temas 0.6, güncellik 1.0, uzunluk 0.183, fit 0.952, yakınlık 1.0] | Temaslar: 14-07-26, 30-07-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 23-06-26 → 28-08-26 | Skor=0.786 [temas 0.667, güncellik 1.0, uzunluk 0.157, fit 0.78, yakınlık 1.0] | Temaslar: 23-06-26, 17-08-26, 28-08-26, 10-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AKFGY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>75</v>
+      </c>
+      <c r="G20" t="n">
+        <v>75</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>9</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>21-09-26</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>CMO, MFI, MOM, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>6</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Genişleyen formasyon (megafon)</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 24-04-26 → 21-09-26 | Skor=0.807 [temas 0.667, güncellik 1.0, uzunluk 0.333, fit 0.901, yakınlık 1.0] | Temaslar: 24-04-26, 30-04-26, 11-06-26, 21-09-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 03-06-26 → 11-09-26 | Skor=0.813 [temas 0.714, güncellik 1.0, uzunluk 0.237, fit 0.8, yakınlık 1.0] | Temaslar: 03-06-26, 10-06-26, 18-06-26, 29-06-26, 11-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AKFIS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>70</v>
+      </c>
+      <c r="G21" t="n">
+        <v>70</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>CCI:HID BEAR, RSI:HID BEAR, Williams %R:HID BEAR</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>02-10-26</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>ATR, Chaikin</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>ADX, CMO, MACD, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>CCI, RSI, Williams %R</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>7</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Daralan (simetrik) üçgen</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 22-05-26 → 17-09-26 | Skor=0.770 [temas 0.6, güncellik 1.0, uzunluk 0.267, fit 0.871, yakınlık 1.0] | Temaslar: 22-05-26, 25-06-26, 17-09-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 28-08-26 → 02-10-26 | Skor=0.679 [temas 0.5, güncellik 1.0, uzunluk 0.083, fit 0.5, yakınlık 1.0] | Temaslar: 28-08-26, 02-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AKFYE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="G22" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>CCI, MFI, MOM, OBV, ROC, RSI</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>ADX, ATR, CMO, MACD</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>10</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç yatay)</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>6 temas (Güçlü) | 29-07-26 → 30-09-26 | Skor=0.818 [temas 0.75, güncellik 1.0, uzunluk 0.15, fit 0.734, yakınlık 1.0] | Temaslar: 29-07-26, 05-08-26, 11-08-26, 19-08-26, 21-09-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 09-06-26 → 10-09-26 | Skor=0.767 [temas 0.6, güncellik 1.0, uzunluk 0.22, fit 0.855, yakınlık 1.0] | Temaslar: 09-06-26, 21-07-26, 10-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AKGRT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>60</v>
+      </c>
+      <c r="G23" t="n">
+        <v>60</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MACD, MFI, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>ADX, MOM, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>6</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 11-11-25 → 30-09-26 | Skor=0.836 [temas 0.714, güncellik 1.0, uzunluk 0.74, fit 0.78, yakınlık 1.0] | Temaslar: 11-11-25, 14-11-25, 01-12-25, 05-12-25, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 09-07-26 → 09-09-26 | Skor=0.787 [temas 0.714, güncellik 1.0, uzunluk 0.143, fit 0.584, yakınlık 1.0] | Temaslar: 09-07-26, 21-07-26, 31-07-26, 31-08-26, 09-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AKHAN</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="G24" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>4</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>24-09-26</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Chaikin, MFI, MOM, OBV</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>CMO, CCI, RSI</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>7</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>İnen üçgen (descending triangle)</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 18-03-26 → 01-10-26 | Skor=0.775 [temas 0.667, güncellik 1.0, uzunluk 0.443, fit 0.525, yakınlık 1.0] | Temaslar: 18-03-26, 30-03-26, 24-09-26, 01-10-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 08-09-26 → 28-09-26 | Skor=0.677 [temas 0.5, güncellik 1.0, uzunluk 0.047, fit 0.5, yakınlık 1.0] | Temaslar: 08-09-26, 28-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AKMGY</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>KARMA</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" t="n">
+        <v>50</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>25-09-26</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Chaikin, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>CCI, MFI, Stochastic</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>İnen üçgen (descending triangle)</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 08-01-26 → 21-09-26 | Skor=0.843 [temas 0.714, güncellik 1.0, uzunluk 0.58, fit 0.924, yakınlık 1.0] | Temaslar: 08-01-26, 15-01-26, 02-03-26, 16-03-26, 21-09-26</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 10-09-26 → 25-09-26 | Skor=0.677 [temas 0.5, güncellik 1.0, uzunluk 0.037, fit 0.5, yakınlık 1.0] | Temaslar: 10-09-26, 25-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AKSA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>80</v>
+      </c>
+      <c r="G26" t="n">
+        <v>80</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>6</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>23-09-26</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>MFI, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>CMO, MACD, RSI</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>ADX, ATR</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>8</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 26-06-26 → 30-09-26 | Skor=0.812 [temas 0.714, güncellik 1.0, uzunluk 0.223, fit 0.796, yakınlık 1.0] | Temaslar: 26-06-26, 09-07-26, 02-09-26, 16-09-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 03-08-26 → 23-09-26 | Skor=0.762 [temas 0.6, güncellik 1.0, uzunluk 0.123, fit 0.854, yakınlık 1.0] | Temaslar: 03-08-26, 08-09-26, 23-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="G27" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" t="n">
+        <v>6</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ATR:HID BEAR, CCI:HID BEAR, Chaikin:HID BEAR, MOM:HID BEAR, ROC:HID BEAR, Williams %R:HID BEAR</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>02-10-26</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>MFI, OBV, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>CMO</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>ATR, CCI, Chaikin, MOM, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>5</v>
+      </c>
+      <c r="X27" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>İnen üçgen (descending triangle)</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 14-11-25 → 17-09-26 | Skor=0.624 [temas 0.6, güncellik 0.958, uzunluk 0.7, fit 0.818, yakınlık 0.23] | Temaslar: 14-11-25, 26-11-25, 17-09-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 17-08-26 → 02-10-26 | Skor=0.778 [temas 0.667, güncellik 1.0, uzunluk 0.113, fit 0.725, yakınlık 1.0] | Temaslar: 17-08-26, 28-08-26, 09-09-26, 02-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AKSGY</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G28" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>MOM:HID BEAR</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>29-09-26</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>MFI, OBV</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>CMO, RSI</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>ATR, CCI, Chaikin, MACD, ROC</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>MOM, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>4</v>
+      </c>
+      <c r="X28" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>İnen üçgen (descending triangle)</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 22-12-25 → 21-09-26 | Skor=0.679 [temas 0.667, güncellik 0.958, uzunluk 0.62, fit 0.737, yakınlık 0.413] | Temaslar: 22-12-25, 26-12-25, 02-03-26, 21-09-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 27-08-26 → 29-09-26 | Skor=0.746 [temas 0.6, güncellik 1.0, uzunluk 0.077, fit 0.721, yakınlık 1.0] | Temaslar: 27-08-26, 11-09-26, 29-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AKSUE</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>80</v>
+      </c>
+      <c r="G29" t="n">
+        <v>80</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>24-09-26</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>ATR, CCI, MOM, OBV</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>MFI</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>4</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 06-02-26 → 01-10-26 | Skor=0.810 [temas 0.667, güncellik 1.0, uzunluk 0.537, fit 0.831, yakınlık 1.0] | Temaslar: 06-02-26, 13-02-26, 19-02-26, 01-10-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 26-08-26 → 24-09-26 | Skor=0.679 [temas 0.5, güncellik 1.0, uzunluk 0.07, fit 0.5, yakınlık 1.0] | Temaslar: 26-08-26, 24-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AKYHO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G30" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>01-10-26</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>ADX, CMO, CCI, Chaikin, RSI</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>2</v>
+      </c>
+      <c r="X30" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>6 temas (Güçlü) | 17-10-25 → 21-09-26 | Skor=0.845 [temas 0.75, güncellik 1.0, uzunluk 0.77, fit 0.687, yakınlık 1.0] | Temaslar: 17-10-25, 18-12-25, 23-12-25, 26-12-25, 02-03-26, 21-09-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 10-09-26 → 01-10-26 | Skor=0.677 [temas 0.5, güncellik 1.0, uzunluk 0.05, fit 0.5, yakınlık 1.0] | Temaslar: 10-09-26, 01-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ALARK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>105</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="G31" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>MACD:HID BULL</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin, MFI, OBV</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>CMO, CCI, MACD, MOM, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>ATR, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>10</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>İnen üçgen (descending triangle)</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 23-03-26 → 30-09-26 | Skor=0.820 [temas 0.714, güncellik 1.0, uzunluk 0.433, fit 0.773, yakınlık 1.0] | Temaslar: 23-03-26, 27-03-26, 07-04-26, 22-05-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 09-09-26 → 24-09-26 | Skor=0.677 [temas 0.5, güncellik 1.0, uzunluk 0.037, fit 0.5, yakınlık 1.0] | Temaslar: 09-09-26, 24-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ALBRK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>75</v>
+      </c>
+      <c r="G32" t="n">
+        <v>75</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>23-09-26</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>OBV</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>3</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Daralan (simetrik) üçgen</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 16-09-26 → 30-09-26 | Skor=0.677 [temas 0.5, güncellik 1.0, uzunluk 0.033, fit 0.5, yakınlık 1.0] | Temaslar: 16-09-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 24-08-26 → 23-09-26 | Skor=0.679 [temas 0.5, güncellik 1.0, uzunluk 0.073, fit 0.5, yakınlık 1.0] | Temaslar: 24-08-26, 23-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ALBTN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>100</v>
+      </c>
+      <c r="G33" t="n">
+        <v>100</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Chaikin, OBV</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 04-09-26 → 30-09-26 | Skor=0.744 [temas 0.6, güncellik 1.0, uzunluk 0.06, fit 0.71, yakınlık 1.0] | Temaslar: 04-09-26, 21-09-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 25-08-26 → 08-09-26 | Skor=0.747 [temas 0.6, güncellik 1.0, uzunluk 0.033, fit 0.75, yakınlık 1.0] | Temaslar: 25-08-26, 01-09-26, 08-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ALCAR</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>608.5</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>80</v>
+      </c>
+      <c r="G34" t="n">
+        <v>80</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>MFI:REG BULL</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>CMO, MFI, MOM, OBV, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>8</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 21-08-26 → 30-09-26 | Skor=0.792 [temas 0.667, güncellik 1.0, uzunluk 0.093, fit 0.875, yakınlık 1.0] | Temaslar: 21-08-26, 02-09-26, 21-09-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 14-09-26 → 02-10-26 | Skor=0.677 [temas 0.5, güncellik 1.0, uzunluk 0.047, fit 0.5, yakınlık 1.0] | Temaslar: 14-09-26, 02-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ALCTL</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="G35" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>9</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>21-09-26</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Chaikin, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>CCI, MFI</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>6 temas (Güçlü) | 14-11-25 → 30-09-26 | Skor=0.854 [temas 0.75, güncellik 1.0, uzunluk 0.73, fit 0.804, yakınlık 1.0] | Temaslar: 14-11-25, 28-11-25, 05-12-25, 29-12-25, 08-01-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>2 temas (Zayıf) | 30-06-26 → 07-09-26 | Skor=0.683 [temas 0.5, güncellik 1.0, uzunluk 0.16, fit 0.5, yakınlık 1.0] | Temaslar: 30-06-26, 07-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ALFAS</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>UYUMSUZLUK</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Williams %R:HID BEAR</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>02-10-26</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>OBV</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>7 temas (Güçlü) | 30-12-25 → 29-09-26 | Skor=0.853 [temas 0.778, güncellik 1.0, uzunluk 0.62, fit 0.721, yakınlık 1.0] | Temaslar: 30-12-25, 08-01-26, 02-03-26, 09-03-26, 23-03-26, 30-03-26, 29-09-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 09-06-26 → 02-10-26 | Skor=0.789 [temas 0.667, güncellik 1.0, uzunluk 0.273, fit 0.752, yakınlık 1.0] | Temaslar: 09-06-26, 21-08-26, 10-09-26, 02-10-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ALGYO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G37" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>01-10-26</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MFI, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>CCI, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>6</v>
+      </c>
+      <c r="X37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 23-03-26 → 01-10-26 | Skor=0.819 [temas 0.714, güncellik 1.0, uzunluk 0.437, fit 0.758, yakınlık 1.0] | Temaslar: 23-03-26, 13-07-26, 03-08-26, 11-08-26, 01-10-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 18-05-26 → 10-09-26 | Skor=0.777 [temas 0.6, güncellik 1.0, uzunluk 0.26, fit 0.94, yakınlık 1.0] | Temaslar: 18-05-26, 03-06-26, 10-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ALKA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>75</v>
+      </c>
+      <c r="G38" t="n">
+        <v>75</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Chaikin, MFI, Stochastic</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Williams %R</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>3</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Düşen kanal</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 18-06-26 → 30-09-26 | Skor=0.801 [temas 0.667, güncellik 1.0, uzunluk 0.243, fit 0.884, yakınlık 1.0] | Temaslar: 18-06-26, 26-06-26, 13-07-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 08-04-26 → 08-09-26 | Skor=0.770 [temas 0.667, güncellik 1.0, uzunluk 0.34, fit 0.527, yakınlık 1.0] | Temaslar: 08-04-26, 13-05-26, 23-07-26, 08-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ALKIM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="G39" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>9</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>21-09-26</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>MFI, OBV</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>CMO, CCI, Chaikin, MACD, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek dusen, direnç dusen)</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>3 temas (Güçlü) | 09-03-26 → 30-09-26 | Skor=0.787 [temas 0.6, güncellik 1.0, uzunluk 0.463, fit 0.935, yakınlık 1.0] | Temaslar: 09-03-26, 16-03-26, 30-09-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 17-06-26 → 08-09-26 | Skor=0.781 [temas 0.667, güncellik 1.0, uzunluk 0.193, fit 0.711, yakınlık 1.0] | Temaslar: 17-06-26, 16-07-26, 22-07-26, 08-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ALKLC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="G40" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>24</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>28-08-26</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MFI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>ATR, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>5</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Düzensiz (destek yukselen, direnç yukselen)</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 04-06-26 → 28-08-26 | Skor=0.808 [temas 0.714, güncellik 1.0, uzunluk 0.2, fit 0.765, yakınlık 1.0] | Temaslar: 04-06-26, 11-06-26, 19-06-26, 26-06-26, 28-08-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 10-06-26 → 16-09-26 | Skor=0.819 [temas 0.714, güncellik 1.0, uzunluk 0.23, fit 0.86, yakınlık 1.0] | Temaslar: 10-06-26, 15-06-26, 08-07-26, 16-07-26, 16-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G41" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>YOK</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>4</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>28-09-26</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>MOM, ROC</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>ADX, CCI</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>CMO, Chaikin, MACD, MFI, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="W41" t="n">
+        <v>4</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Daralan (simetrik) üçgen</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>4 temas (Güçlü) | 20-07-26 → 28-09-26 | Skor=0.789 [temas 0.667, güncellik 1.0, uzunluk 0.167, fit 0.802, yakınlık 1.0] | Temaslar: 20-07-26, 30-07-26, 04-08-26, 28-09-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>5 temas (Güçlü) | 07-01-26 → 02-10-26 | Skor=0.818 [temas 0.714, güncellik 1.0, uzunluk 0.613, fit 0.658, yakınlık 1.0] | Temaslar: 07-01-26, 24-08-26, 04-09-26, 18-09-26, 02-10-26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC6"/>
+  <autoFilter ref="A1:AC41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1404,7 +6165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1413,8 +6174,8 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
@@ -1501,7 +6262,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MACD, CCI, Chaikin, MFI, Stochastic, Williams %R</t>
+          <t>CCI, Chaikin, MACD, MFI, Stochastic, Williams %R</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1520,7 +6281,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>24.9</v>
+        <v>24.92</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -1531,7 +6292,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>AFYON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1540,7 +6301,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1548,16 +6309,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MACD, Chaikin, OBV, Stochastic</t>
+          <t>Chaikin, MFI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADX</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1567,11 +6328,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Williams %R</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>89.15000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -1582,28 +6343,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A1CAP</t>
+          <t>ALBTN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>YÜKSEK</t>
+          <t>DÜŞÜK</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>RSI</t>
+          <t>Chaikin, OBV</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1618,31 +6379,31 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CCI, Chaikin, MFI, Stochastic, Williams %R</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>4.67</v>
+        <v>23.44</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SATIM</t>
+          <t>ALIM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>AKFYE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83.33</v>
+        <v>90.91</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1650,16 +6411,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MACD</t>
+          <t>CCI, MFI, MOM, OBV, ROC, RSI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADX, ATR, CMO, MACD</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1669,71 +6430,1601 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>RSI, CCI, Chaikin, MFI, Williams %R</t>
+          <t>Chaikin</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>8.94</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SATIM</t>
+          <t>ALIM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>AKCNS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>MACD, MFI, MOM, ROC, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AGESA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ADX, ATR, CMO, Chaikin, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Stochastic</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>238</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ALCTL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Chaikin, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CCI, MFI</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ACSEL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Chaikin, MACD, MOM, OBV, Stochastic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Williams %R</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>89.65000000000001</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AKSUE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>80</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ATR, CCI, MOM, OBV</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MFI</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AKSA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>80</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>MFI, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>CMO, MACD, RSI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ADX, ATR</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ALCAR</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>80</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CMO, MFI, MOM, OBV, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>608.5</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AKHAN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Chaikin, MFI, MOM, OBV</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>CMO, CCI, RSI</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ALARK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin, MFI, OBV</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>CMO, CCI, MACD, MOM, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ATR, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>105</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ALBRK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>75</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OBV</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ALKA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>75</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Chaikin, MFI, Stochastic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Williams %R</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AKFGY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>75</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CMO, MFI, MOM, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ADGYO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CCI, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ATR, Chaikin</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AKFIS</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>70</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ATR, Chaikin</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ADX, CMO, MACD, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>CCI, RSI, Williams %R</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ALGYO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MFI, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>CCI, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AGROT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MFI, MOM, RSI</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CCI, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AKENR</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin, MFI, MOM, OBV, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CMO, CCI, ROC, RSI</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ALFAS</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>OBV</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MACD, MFI, OBV, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ADX, CCI, MOM, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AGYO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>60</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>CMO, Chaikin, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>CCI, MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AKGRT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>60</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MACD, MFI, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ADX, MOM, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ALIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AHGAZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>100</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ATR, CMO, MACD, RSI</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MFI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AGHOL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>19</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ATR, CMO, CCI, Chaikin, MOM, OBV, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>32.36</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AHSGY</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>15</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CCI, MACD</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ADX, CMO, Chaikin, MOM, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>AAGYO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>80</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>MACD, ROC</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ADX, CMO, CCI, Chaikin, MFI, MOM, RSI, Williams %R</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ALKIM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MFI, OBV</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CMO, CCI, Chaikin, MACD, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>AKYHO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ADX, CMO, CCI, Chaikin, RSI</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>MOM, ROC</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ADX, CCI</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CMO, Chaikin, MACD, MFI, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AKSGY</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>MFI, OBV</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>CMO, RSI</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ATR, CCI, Chaikin, MACD, ROC</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>MOM, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>A1YEN</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>BEARISH</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C35" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>ORTA</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E35" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Chaikin, MFI</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>RSI, MACD, CCI, Stochastic</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ATR, Chaikin, MFI</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CCI, MACD, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>SATIM</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ADESE</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>60</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CCI, MFI, Williams %R</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>SATIM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K6"/>
+  <autoFilter ref="A1:K36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1744,7 +8035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1758,9 +8049,9 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="38" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="37" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
@@ -1844,7 +8135,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A1YEN</t>
+          <t>A1CAP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1858,35 +8149,35 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.77</v>
+        <v>4.67</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BEARISH</t>
+          <t>KARMA</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ORTA</t>
+          <t>DÜŞÜK</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30-09-26</t>
+          <t>01-10-26</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Chaikin, MFI</t>
+          <t>ATR, CMO, MOM, ROC, RSI</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1901,17 +8192,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>RSI, MACD, CCI, Stochastic</t>
+          <t>CCI, Chaikin, MFI, Stochastic, Williams %R</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>A1YEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1925,7 +8216,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.94</v>
+        <v>1.78</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1933,27 +8224,27 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>83.33</v>
+        <v>62.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>YÜKSEK</t>
+          <t>ORTA</t>
         </is>
       </c>
       <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>02-10-26</t>
+          <t>30-09-26</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>MACD</t>
+          <t>ATR, Chaikin, MFI</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1963,22 +8254,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADX</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>RSI, CCI, Chaikin, MFI, Williams %R</t>
+          <t>CCI, MACD, RSI, Stochastic</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACSEL</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1992,11 +8283,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>89.15000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BULLISH</t>
+          <t>BEARISH</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -2008,19 +8299,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>29-09-26</t>
+          <t>02-10-26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MACD, Chaikin, OBV, Stochastic</t>
+          <t>MACD, ROC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2035,17 +8326,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Williams %R</t>
+          <t>ADX, CMO, CCI, Chaikin, MFI, MOM, RSI, Williams %R</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADEL</t>
+          <t>ACSEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2059,7 +8350,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.9</v>
+        <v>89.65000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2067,7 +8358,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2075,19 +8366,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30-09-26</t>
+          <t>29-09-26</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>MACD, CCI, Chaikin, MFI, Stochastic, Williams %R</t>
+          <t>Chaikin, MACD, MOM, OBV, Stochastic</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2102,15 +8393,1958 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Williams %R</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>6</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADEL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MACD, MFI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADESE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>01-10-26</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>CCI, MFI, Williams %R</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADGYO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>24-09-26</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>CCI, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ATR, Chaikin</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AEFES</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MACD, MFI, OBV, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ADX, CCI, MOM, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AFYON</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Chaikin, MFI</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ADX</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AGROT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MFI, MOM, RSI</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>CCI, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AGYO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>29-09-26</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>CMO, Chaikin, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>CCI, MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AHGAZ</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>45.78</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>25-09-26</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ATR, CMO, MACD, RSI</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MFI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AKBNK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>KARMA</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CCI, MACD, MFI, Stochastic</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ADX, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>CMO, RSI</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AKCNS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>85.70999999999999</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>22-09-26</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>MACD, MFI, MOM, ROC, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AKENR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin, MFI, MOM, OBV, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>CMO, CCI, ROC, RSI</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AKFIS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>70</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>02-10-26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ATR, Chaikin</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ADX, CMO, MACD, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>CCI, RSI, Williams %R</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AKFYE</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>90.91</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>CCI, MFI, MOM, OBV, ROC, RSI</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>ADX, ATR, CMO, MACD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Chaikin</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AKGRT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MACD, MFI, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>ADX, MOM, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AKHAN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>77.78</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24-09-26</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Chaikin, MFI, MOM, OBV</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>CMO, CCI, RSI</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AKMGY</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>KARMA</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>50</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>25-09-26</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Chaikin, MOM, ROC</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>CCI, MFI, Stochastic</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AKSA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>80</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>23-09-26</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>MFI, MOM, ROC, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>CMO, MACD, RSI</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>ADX, ATR</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AKSEN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>02-10-26</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>MFI, OBV, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>CMO</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>ATR, CCI, Chaikin, MOM, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AKSGY</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>29-09-26</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>MFI, OBV</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>CMO, RSI</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>ATR, CCI, Chaikin, MACD, ROC</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>MOM, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AKSUE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>80</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>24-09-26</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ATR, CCI, MOM, OBV</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>MFI</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AKYHO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>01-10-26</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>ADX, CMO, CCI, Chaikin, RSI</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ALARK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>105</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ADX, Chaikin, MFI, OBV</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>CMO, CCI, MACD, MOM, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>ATR, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ALBRK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>75</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>23-09-26</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>OBV</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ALBTN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>100</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DÜŞÜK</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Chaikin, OBV</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ALCAR</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>608.5</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>80</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>YÜKSEK</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>CMO, MFI, MOM, OBV, ROC, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ALFAS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>02-10-26</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>CCI, Chaikin, MACD, MFI, RSI</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>OBV</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ALGYO</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>01-10-26</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ATR, CMO, Chaikin, MFI, RSI, Stochastic</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>CCI, ROC, Williams %R</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ALKA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>75</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>30-09-26</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Chaikin, MFI, Stochastic</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Williams %R</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ALTIN</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>06-10-26</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>BEARISH</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ORTA</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>6</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>28-09-26</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>MOM, ROC</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>ADX, CCI</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>CMO, Chaikin, MACD, MFI, RSI, Stochastic, Williams %R</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O5"/>
+  <autoFilter ref="A1:O34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>